--- a/output/pdf_financials_xlsx/CJR.B.xlsx
+++ b/output/pdf_financials_xlsx/CJR.B.xlsx
@@ -60812,7 +60812,7 @@
       </c>
       <c r="D494" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E494" t="inlineStr">
@@ -65916,7 +65916,7 @@
       </c>
       <c r="D545" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E545" t="inlineStr">
@@ -68218,7 +68218,7 @@
       </c>
       <c r="D567" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E567" t="inlineStr">
@@ -70412,7 +70412,7 @@
       </c>
       <c r="D588" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E588" t="inlineStr">
@@ -74648,7 +74648,7 @@
       </c>
       <c r="D628" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E628" t="inlineStr">
@@ -82394,7 +82394,7 @@
       </c>
       <c r="D701" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E701" s="5" t="n">

--- a/output/pdf_financials_xlsx/CJR.B.xlsx
+++ b/output/pdf_financials_xlsx/CJR.B.xlsx
@@ -1667,10 +1667,10 @@
         </is>
       </c>
       <c r="F20" s="3" t="n">
-        <v>148.681</v>
+        <v>156.151</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>159.895</v>
+        <v>165.749</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>156.169</v>
@@ -1679,7 +1679,7 @@
         <v>-19.5</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>191.665</v>
+        <v>224.089</v>
       </c>
       <c r="K20" s="3" t="n">
         <v>224.089</v>
@@ -1862,10 +1862,10 @@
         </is>
       </c>
       <c r="F23" s="3" t="n">
-        <v>148.681</v>
+        <v>156.151</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>159.895</v>
+        <v>165.749</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>156.169</v>
@@ -1874,7 +1874,7 @@
         <v>-19.5</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>191.665</v>
+        <v>224.089</v>
       </c>
       <c r="K23" s="3" t="n">
         <v>224.089</v>
@@ -2115,7 +2115,7 @@
         </is>
       </c>
       <c r="F26" s="3" t="n">
-        <v>83.062011</v>
+        <v>87.235196</v>
       </c>
       <c r="G26" s="1" t="inlineStr">
         <is>
@@ -2543,10 +2543,10 @@
         </is>
       </c>
       <c r="F32" s="3" t="n">
-        <v>17.65228974825354</v>
+        <v>18.53917243278925</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>21.27576057567435</v>
+        <v>22.05469864384407</v>
       </c>
       <c r="H32" s="3" t="n">
         <v>18.74741901716174</v>
@@ -2555,7 +2555,7 @@
         <v>-2.391713632154444</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>11.41537145743201</v>
+        <v>13.34651174979512</v>
       </c>
       <c r="K32" s="3" t="n">
         <v>13.34651174979512</v>
@@ -9045,13 +9045,13 @@
         </is>
       </c>
       <c r="B126" s="3" t="n">
-        <v>-46.284</v>
+        <v>-48.026</v>
       </c>
       <c r="C126" s="3" t="n">
-        <v>-48.021</v>
+        <v>-51.015</v>
       </c>
       <c r="D126" s="3" t="n">
-        <v>-44.605</v>
+        <v>-54.825</v>
       </c>
       <c r="E126" s="1" t="inlineStr">
         <is>
@@ -9059,37 +9059,37 @@
         </is>
       </c>
       <c r="F126" s="3" t="n">
-        <v>-50.783</v>
+        <v>-56.836</v>
       </c>
       <c r="G126" s="3" t="n">
-        <v>-56.696</v>
+        <v>-69.358</v>
       </c>
       <c r="H126" s="3" t="n">
-        <v>-65.474</v>
+        <v>-72.211</v>
       </c>
       <c r="I126" s="3" t="n">
-        <v>-76.22799999999999</v>
+        <v>-81.831</v>
       </c>
       <c r="J126" s="3" t="n">
-        <v>-89.702</v>
+        <v>-109.526</v>
       </c>
       <c r="K126" s="3" t="n">
-        <v>-106.062</v>
+        <v>-141.088</v>
       </c>
       <c r="L126" s="3" t="n">
-        <v>-198.808</v>
+        <v>-227.617</v>
       </c>
       <c r="M126" s="3" t="n">
-        <v>-38.15</v>
+        <v>-68.515</v>
       </c>
       <c r="N126" s="3" t="n">
-        <v>-50.399</v>
+        <v>-70.38200000000001</v>
       </c>
       <c r="O126" s="3" t="n">
-        <v>-49.991</v>
+        <v>-67.667</v>
       </c>
       <c r="P126" s="3" t="n">
-        <v>-49.561</v>
+        <v>-69.333</v>
       </c>
       <c r="Q126" s="1" t="inlineStr">
         <is>
@@ -35982,7 +35982,11 @@
           <t>Dividends paid to non-controlling interest</t>
         </is>
       </c>
-      <c r="D255" t="inlineStr"/>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>CashDividendsPaid</t>
+        </is>
+      </c>
       <c r="E255" t="inlineStr">
         <is>
           <t>-</t>
@@ -48118,7 +48122,11 @@
           <t>Dividends paid to non-controlling interest (6,331)</t>
         </is>
       </c>
-      <c r="D372" t="inlineStr"/>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>CashDividendsPaid</t>
+        </is>
+      </c>
       <c r="E372" t="inlineStr">
         <is>
           <t>-</t>
@@ -55334,7 +55342,11 @@
           <t>Dividend paid to non-controlling interest</t>
         </is>
       </c>
-      <c r="D441" t="inlineStr"/>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>CashDividendsPaid</t>
+        </is>
+      </c>
       <c r="E441" s="5" t="n">
         <v>-1.742</v>
       </c>
@@ -66766,11 +66778,7 @@
           <t>Shareholders</t>
         </is>
       </c>
-      <c r="D553" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+      <c r="D553" t="inlineStr"/>
       <c r="E553" t="inlineStr">
         <is>
           <t>-</t>
@@ -75724,11 +75732,7 @@
           <t>Shareholders 150,408</t>
         </is>
       </c>
-      <c r="D638" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+      <c r="D638" t="inlineStr"/>
       <c r="E638" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/CJR.B.xlsx
+++ b/output/pdf_financials_xlsx/CJR.B.xlsx
@@ -4758,63 +4758,55 @@
         </is>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>65.74299999999999</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>89.06100000000001</v>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>90.61</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
+        <v>78.39700000000001</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0</v>
+        <v>70.55200000000001</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0</v>
+        <v>86.023</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0</v>
+        <v>77.64</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0</v>
+        <v>183.141</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>0</v>
+        <v>162.384</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>0</v>
+        <v>136.952</v>
       </c>
       <c r="M64" s="3" t="n">
-        <v>0</v>
+        <v>160.088</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>0</v>
+        <v>113.754</v>
       </c>
       <c r="O64" s="3" t="n">
-        <v>0</v>
+        <v>171.165</v>
       </c>
       <c r="P64" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>136.36</v>
+      </c>
+      <c r="Q64" s="3" t="n">
+        <v>156.236</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>160.649</v>
+      </c>
+      <c r="S64" s="3" t="n">
+        <v>125.967</v>
       </c>
     </row>
     <row r="65">
@@ -5085,20 +5077,14 @@
       <c r="P68" s="3" t="n">
         <v>526.899</v>
       </c>
-      <c r="Q68" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R68" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S68" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Q68" s="3" t="n">
+        <v>156.236</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>160.649</v>
+      </c>
+      <c r="S68" s="3" t="n">
+        <v>125.967</v>
       </c>
     </row>
     <row r="69">
@@ -7734,13 +7720,13 @@
         </is>
       </c>
       <c r="B107" s="3" t="n">
-        <v>0</v>
+        <v>1.917</v>
       </c>
       <c r="C107" s="3" t="n">
-        <v>0</v>
+        <v>1.314</v>
       </c>
       <c r="D107" s="3" t="n">
-        <v>0</v>
+        <v>0.907</v>
       </c>
       <c r="E107" s="1" t="inlineStr">
         <is>
@@ -7748,37 +7734,37 @@
         </is>
       </c>
       <c r="F107" s="3" t="n">
-        <v>0</v>
+        <v>1.158</v>
       </c>
       <c r="G107" s="3" t="n">
-        <v>0</v>
+        <v>3.172</v>
       </c>
       <c r="H107" s="3" t="n">
-        <v>0</v>
+        <v>2.026</v>
       </c>
       <c r="I107" s="3" t="n">
-        <v>0</v>
+        <v>2.176</v>
       </c>
       <c r="J107" s="3" t="n">
-        <v>0</v>
+        <v>0.973</v>
       </c>
       <c r="K107" s="3" t="n">
-        <v>0</v>
+        <v>1.005</v>
       </c>
       <c r="L107" s="3" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="M107" s="3" t="n">
-        <v>0</v>
+        <v>0.699</v>
       </c>
       <c r="N107" s="3" t="n">
-        <v>0</v>
+        <v>1.112</v>
       </c>
       <c r="O107" s="3" t="n">
-        <v>0</v>
+        <v>1.106</v>
       </c>
       <c r="P107" s="3" t="n">
-        <v>0</v>
+        <v>1.265</v>
       </c>
       <c r="Q107" s="1" t="inlineStr">
         <is>
@@ -7820,10 +7806,10 @@
         <v>0</v>
       </c>
       <c r="G108" s="3" t="n">
-        <v>0</v>
+        <v>4.24</v>
       </c>
       <c r="H108" s="3" t="n">
-        <v>0</v>
+        <v>78.45999999999999</v>
       </c>
       <c r="I108" s="3" t="n">
         <v>0</v>
@@ -8700,10 +8686,10 @@
         </is>
       </c>
       <c r="B121" s="3" t="n">
-        <v>0</v>
+        <v>-91.444</v>
       </c>
       <c r="C121" s="3" t="n">
-        <v>0</v>
+        <v>-15.083</v>
       </c>
       <c r="D121" s="3" t="n">
         <v>0</v>
@@ -8714,10 +8700,10 @@
         </is>
       </c>
       <c r="F121" s="3" t="n">
-        <v>0</v>
+        <v>-25.295</v>
       </c>
       <c r="G121" s="3" t="n">
-        <v>0</v>
+        <v>-1.464</v>
       </c>
       <c r="H121" s="3" t="n">
         <v>0</v>
@@ -33494,7 +33480,11 @@
           <t>Deferred income tax expense (recovery) (note 21)</t>
         </is>
       </c>
-      <c r="D230" t="inlineStr"/>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E230" t="inlineStr">
         <is>
           <t>-</t>
@@ -33704,7 +33694,11 @@
           <t>Share-based compensation expense (note 16)</t>
         </is>
       </c>
-      <c r="D232" t="inlineStr"/>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E232" t="inlineStr">
         <is>
           <t>-</t>
@@ -38782,7 +38776,11 @@
           <t>Deferred income taxes (recovery) (note 21)</t>
         </is>
       </c>
-      <c r="D283" t="inlineStr"/>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E283" t="inlineStr">
         <is>
           <t>-</t>
@@ -41396,7 +41394,11 @@
           <t>Share-based compensation expense (note 15)</t>
         </is>
       </c>
-      <c r="D308" t="inlineStr"/>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E308" t="inlineStr">
         <is>
           <t>-</t>
@@ -43382,7 +43384,11 @@
           <t>Broadcast license and goodwill impairment charges</t>
         </is>
       </c>
-      <c r="D327" t="inlineStr"/>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>AssetImpairmentCharge</t>
+        </is>
+      </c>
       <c r="E327" t="inlineStr">
         <is>
           <t>-</t>
@@ -43486,7 +43492,11 @@
           <t>Capital asset impairment charges</t>
         </is>
       </c>
-      <c r="D328" t="inlineStr"/>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>AssetImpairmentCharge</t>
+        </is>
+      </c>
       <c r="E328" t="inlineStr">
         <is>
           <t>-</t>
@@ -43908,7 +43918,11 @@
           <t>Impact of investment impairment charges</t>
         </is>
       </c>
-      <c r="D332" t="inlineStr"/>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>AssetImpairmentCharge</t>
+        </is>
+      </c>
       <c r="E332" t="inlineStr">
         <is>
           <t>-</t>
@@ -45904,7 +45918,11 @@
           <t>Share-based compensation expense 1,586</t>
         </is>
       </c>
-      <c r="D351" t="inlineStr"/>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E351" t="inlineStr">
         <is>
           <t>-</t>
@@ -49718,7 +49736,11 @@
           <t>Share-based compensation expense (note 15)</t>
         </is>
       </c>
-      <c r="D387" t="inlineStr"/>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E387" t="inlineStr">
         <is>
           <t>-</t>
@@ -51278,7 +51300,11 @@
           <t>Shares repurchased (note 15)</t>
         </is>
       </c>
-      <c r="D402" t="inlineStr"/>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E402" t="inlineStr">
         <is>
           <t>-</t>
@@ -53168,7 +53194,11 @@
           <t>Future income taxes</t>
         </is>
       </c>
-      <c r="D420" t="inlineStr"/>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E420" s="5" t="n">
         <v>-7.321</v>
       </c>
@@ -53372,7 +53402,11 @@
           <t>Stock option expense</t>
         </is>
       </c>
-      <c r="D422" t="inlineStr"/>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E422" s="5" t="n">
         <v>1.917</v>
       </c>
@@ -55132,7 +55166,11 @@
           <t>Shares repurchased</t>
         </is>
       </c>
-      <c r="D439" t="inlineStr"/>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E439" s="5" t="n">
         <v>-91.444</v>
       </c>
